--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/en-US.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/en-US.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF13686-0C5C-4E22-91F0-624092317B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5BF13686-0C5C-4E22-91F0-624092317B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D85BA682-A1F8-42F5-AB4B-0E68CE8591FE}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7396,11 +7396,13 @@
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
     </row>
     <row r="10" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="17"/>
@@ -7410,6 +7412,8 @@
       <c r="D10" s="19" t="s">
         <v>5</v>
       </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="20"/>
@@ -7425,6 +7429,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
+      <c r="L11" s="8"/>
     </row>
     <row r="12" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="22"/>
@@ -7440,6 +7445,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C13" s="1"/>
@@ -7450,6 +7456,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
+      <c r="L13" s="8"/>
     </row>
     <row r="14" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C14" s="8"/>
@@ -7692,7 +7699,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <dataConsolidate/>
-  <conditionalFormatting sqref="F9:I1048576 F1:I1 H2:J5">
+  <conditionalFormatting sqref="F14:I1048576 F1:I1 H2:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -7711,7 +7718,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:I9 H6:J8" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J8" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
